--- a/debug/judgements_q_sty_swi/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Qwen3-4B-Instruct-2507/simple/total_votes_file.xlsx
+++ b/debug/judgements_q_sty_swi/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Qwen3-4B-Instruct-2507/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="D2">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="H2">
         <v>852</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D3">
-        <v>590</v>
+        <v>582</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G3">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H3">
         <v>852</v>
